--- a/review_agent/outputs/v4/filter.xlsx
+++ b/review_agent/outputs/v4/filter.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>블루 배차 방식과 고객만 패널티 받는 취소 정책 불만</t>
+          <t>블루 배차 방식과 기사 일방 취소 시 패널티 정책 불만</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -503,7 +503,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>경로 추천 기능 문제</t>
+          <t>경로 추천 기능 불만</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -527,7 +527,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>유료 옵션 상단 노출 등 선택지 노출 방식</t>
+          <t>비싼 블루 택시 상단 노출 방식(선택지 노출) 불만</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -551,7 +551,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>추가 이용료 표시/유도 화면 문제</t>
+          <t>일반 택시 선택 시 이용료 추가되는 요금 표시/정책 불만</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -575,7 +575,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>기사에 대한 불만이며 앱 관련 구체 내용 없음</t>
+          <t>의미 불명확하고 기사에 대한 불만</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -599,7 +599,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>광고·수수료·경로 추천 불만</t>
+          <t>광고, 수수료, 경로 추천 불만</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
@@ -623,7 +623,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>호출/배차 안됨</t>
+          <t>호출 배정이 안 되는 기능 문제</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -647,7 +647,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>배정 방식(먼 택시 배정)</t>
+          <t>가까운 택시가 아닌 먼 택시 배정 방식 불만</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>경로 안내 문제</t>
+          <t>경로 안내 불만</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -695,7 +695,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>일반/블루 배차 차이 문제</t>
+          <t>일반/블루 배차 방식 불만</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>기사에 대한 욕설 비난</t>
+          <t>기사 개인에 대한 욕설 비난</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
@@ -743,7 +743,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>블루파트너 정책/기능 변경 불만</t>
+          <t>블루파트너 기능/정책 변경 불만</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -767,7 +767,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>로그인 유지 오류</t>
+          <t>로그인 풀림 오류</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>기사 개인의 콜 선택 행동 불만</t>
+          <t>기사 개인의 콜 선택 행동에 대한 불만</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -815,7 +815,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>기사 취소에 대한 앱의 불이익 없는 정책</t>
+          <t>기사 취소에 불이익이 없는 취소 정책 불만</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
@@ -839,7 +839,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>특정 기사 행동에 대한 불만</t>
+          <t>특정 택시기사 행동에 대한 불만</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -863,7 +863,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>기사 비하, 앱 관련 내용 없음</t>
+          <t>기사 비하, 앱과 무관한 감정 표현</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
@@ -887,7 +887,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>카카오 바이크 부가 서비스 불만</t>
+          <t>바이크 부가 서비스 불만</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>운행중 택시 배정 방지 기능 요청</t>
+          <t>운행 중인 택시가 배정되는 배차 기능 개선 요청</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
@@ -935,7 +935,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>퀵 배송 부가 서비스 불만</t>
+          <t>퀵 배송 부가 서비스 운영 불만</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>경로 안내 기능 문제</t>
+          <t>경로 안내 기능 불만</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
@@ -983,7 +983,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>도착 예정시간 표시 부정확</t>
+          <t>도착 예정 시간 표시 부정확</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>접속 끊김 및 불편</t>
+          <t>접속 끊김 오류</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>카풀 서비스 재개 및 배차 문제</t>
+          <t>호출 배정 및 카풀 서비스 정책 불만</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>먼 택시 배차 및 취소 문제</t>
+          <t>먼 택시 배차 및 기사 취소 문제</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>경로 추천 문제</t>
+          <t>경로 추천 불만</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>주가 등 회사 전반 비난</t>
+          <t>회사 주가 관련 일반 비난</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>배차 우선순위 방식 개선 요청</t>
+          <t>배차 우선순위 방식 불만</t>
         </is>
       </c>
       <c r="F33" t="inlineStr"/>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>추천경로/요금 표시 및 경로 선택 기능</t>
+          <t>추천 경로/요금 표시 및 경로 선택지 불만</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>호출 배차 방식 문제</t>
+          <t>호출 배차 방식 불만</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GPS/네트워크 오류 및 배정 문제</t>
+          <t>네트워크/GPS 오류와 배차 문제</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>자전거 부가 서비스 기기 상태 불만</t>
+          <t>자전거 부가 서비스 불만</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>배차 거리 방식 변경 불만</t>
+          <t>배차 거리 변경 불만</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>인증번호 미수신</t>
+          <t>인증번호 미수신 오류</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>기사 칭찬</t>
+          <t>기사 서비스 칭찬</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>추천경로 및 요금 정책</t>
+          <t>추천 경로와 요금 정책 불만</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>호출 배차 안됨</t>
+          <t>배차가 안 되는 기능 불만</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>평가 화면 팝업과 배차 문제</t>
+          <t>평가 화면 팝업과 배차 불만</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>예상금액과 실제 결제금액 차이</t>
+          <t>예상 금액 표시와 실제 요금 차이</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>기사의 승객 선택 행동 불만</t>
+          <t>기사의 승객 선택 행동에 대한 불만</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>경로 선택지 부족</t>
+          <t>경로 선택지 부족 불만</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>기사 운행 및 상담 응대 불만, 앱 기능 구체성 없음</t>
+          <t>지정 지점이 기사에게 잘못 전달되는 위치 문제 및 환불/문의 처리</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>기사에게 전달되는 경로 안내 불일치</t>
+          <t>기사에게 안내되는 경로/위치 정보 불일치</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>추천경로 및 요금 문제</t>
+          <t>추천 경로 불만</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>블루 백투백 배차 방식과 환불·취소 정책</t>
+          <t>블루 백투백 배차 방식과 취소·환불 정책 불만</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>일부 기사의 개인 행동에 대한 의심</t>
+          <t>일부 기사의 운행 행동에 대한 불만</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>약관 변경과 사전 고지 방식, 요금 적용</t>
+          <t>약관 변경 사전 고지 부재와 요금 적용 정책</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>주차패스 취소 기능 부재와 환불 정책</t>
+          <t>주차패스 선택 취소 불가 및 환불 정책 불만</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>퀵 부가 서비스 운영 및 기사 불만</t>
+          <t>퀵 부가서비스 및 퀵 기사 행동에 대한 불만</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>앱 문제인지 기사 문제인지 불분명, 구체적 앱 내용 없음</t>
+          <t>출발·도착 지점 표시/전달 문제</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>기사 관리 일반 요청, 구체적 앱 내용 없음</t>
+          <t>구체적 내용 없는 관리 요청</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>대리운전 부가 서비스 평가</t>
+          <t>대리운전 서비스에 대한 칭찬, 앱 평가 아님</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -1895,7 +1895,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>구체적 내용 없는 비난</t>
+          <t>구체적 내용 없는 일반 비난</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>바이크 부가 서비스 운영 불만</t>
+          <t>바이크 부가서비스 운영 불만</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>택시 호출 배차 안됨</t>
+          <t>택시 배차 안 됨</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>갤럭시 기기 연동 호환 문제</t>
+          <t>갤럭시 기기 연동/호환 문제</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>배차 위치 방향 문제</t>
+          <t>반대편 배차 방식 불만</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>배차 취소 시 이용 정지 패널티 정책</t>
+          <t>배차 거절 시 이용 정지 패널티 정책</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>위치 명칭 표시와 추천경로 안내 방식</t>
+          <t>GPS 장소 명칭 표시와 추천경로 안내 불만</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>출발지 임의 변경 오류</t>
+          <t>출발지가 임의 변경되는 기능 문제</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>승차거부 신고 절차와 도착지 정보 표시</t>
+          <t>승차거부 신고 절차와 목적지 표시 시점 불만</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>블루 유도와 배차 방식</t>
+          <t>블루 추가요금 없으면 배차 안 되는 방식</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>수수료 및 환불 정책</t>
+          <t>수수료 부과 및 환불 정책 불만</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>기사 선택·선호사항 설정 기능 요청 및 펫택시 요금</t>
+          <t>기사 선호사항 설정 기능 및 펫택시 요금 불만</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>배차 대기와 기사 취소에 대한 앱 처리</t>
+          <t>배차 지연과 기사 콜 취소 정책</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>기사들 행태와 업계 전반 비난</t>
+          <t>기사들의 행태에 대한 비난</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>추천 경로 문제</t>
+          <t>추천 경로 불만</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>블루 배차 방식 문제</t>
+          <t>블루 운행중 차량 배차 방식</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>배차 실패와 블루 유도 설정</t>
+          <t>배차 실패와 블루 유도 설정 불만</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>기사 취소 패널티·차단 기능 요청</t>
+          <t>기사 취소 패널티 및 차단 기능 요청</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>기사 태도 불만</t>
+          <t>기사 태도 및 운행 불만</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>추천경로 및 배차 방향, 예상요금 차이</t>
+          <t>추천 경로와 배차 방향, 예상요금 불일치</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>배차 및 위치 표시 오류</t>
+          <t>배차 안 됨과 위치 표시 오류</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>호출 배차 안됨</t>
+          <t>택시 배차 안 됨</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>이중결제 처리</t>
+          <t>이중결제 처리 불만</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>내비게이션 우회 경로 안내</t>
+          <t>내비게이션 우회 경로 안내 불만</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>기사 요금 행위 불만이 주</t>
+          <t>기사 미터기·요금 행위에 대한 불만</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>지도 경로 안내 오류와 패널티 정책</t>
+          <t>공사 구간 경로 안내 오류와 패널티 정책</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>탑승 위치 변경 미반영</t>
+          <t>탑승 위치 변경이 반영되지 않는 기능 문제</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>일반택시 호출 배차 제한 의혹</t>
+          <t>일반택시 배차 제한 불만</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>바이크 부가 서비스 반납 문제</t>
+          <t>바이크 부가서비스 반납 오류</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>일반호출 전달 방식과 블루 수수료</t>
+          <t>일반 호출 전달 방식과 블루 수수료 정책</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>바이크 부가 서비스 불만</t>
+          <t>바이크 부가서비스 운영 불만</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
